--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold_generic/plain/mol2mol_scaffold_generic_plain_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold_generic/plain/mol2mol_scaffold_generic_plain_generated_optimal.xlsx
@@ -1070,23 +1070,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:BF19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="32.7109375" customWidth="1"/>
-    <col min="13" max="13" width="28.7109375" customWidth="1"/>
-    <col min="14" max="14" width="37.7109375" customWidth="1"/>
-    <col min="15" max="15" width="38.7109375" customWidth="1"/>
-    <col min="16" max="16" width="30.7109375" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="31.7109375" customWidth="1"/>
+    <col min="13" max="13" width="30.7109375" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" customWidth="1"/>
+    <col min="15" max="15" width="27.7109375" customWidth="1"/>
+    <col min="16" max="16" width="26.7109375" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" customWidth="1"/>
+    <col min="18" max="19" width="22.7109375" customWidth="1"/>
+    <col min="20" max="21" width="20.7109375" customWidth="1"/>
+    <col min="22" max="22" width="24.7109375" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" customWidth="1"/>
+    <col min="25" max="25" width="32.7109375" customWidth="1"/>
+    <col min="26" max="26" width="28.7109375" customWidth="1"/>
+    <col min="27" max="27" width="37.7109375" customWidth="1"/>
+    <col min="28" max="28" width="38.7109375" customWidth="1"/>
+    <col min="29" max="29" width="30.7109375" customWidth="1"/>
+    <col min="30" max="31" width="13.7109375" customWidth="1"/>
+    <col min="32" max="35" width="12.7109375" customWidth="1"/>
+    <col min="36" max="36" width="21.7109375" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" customWidth="1"/>
+    <col min="39" max="39" width="15.7109375" customWidth="1"/>
+    <col min="40" max="42" width="14.7109375" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" customWidth="1"/>
+    <col min="44" max="44" width="20.7109375" customWidth="1"/>
+    <col min="45" max="45" width="13.7109375" customWidth="1"/>
+    <col min="46" max="46" width="17.7109375" customWidth="1"/>
+    <col min="47" max="48" width="12.7109375" customWidth="1"/>
+    <col min="49" max="49" width="15.7109375" customWidth="1"/>
+    <col min="50" max="50" width="18.7109375" customWidth="1"/>
+    <col min="51" max="54" width="12.7109375" customWidth="1"/>
+    <col min="55" max="55" width="18.7109375" customWidth="1"/>
+    <col min="56" max="56" width="23.7109375" customWidth="1"/>
+    <col min="57" max="57" width="25.7109375" customWidth="1"/>
+    <col min="58" max="58" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1122,55 +1151,260 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>qsar_model_count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>qsar_models_used</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>pred_logIC50_uM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pred_ic50_uM</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>pred_pIC50</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pred_logIC50_uM_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pred_logIC50_uM_ensemble_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_ensemble_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_ensemble_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_lower95</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_upper95</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_lower95</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_upper95</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_uncertainty</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>pred_cLogP</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pred_logS_ESOL</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>pred_Solubility_ESOL_mol_per_L</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pred_Solubility_ESOL_class</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Clearance_Microsome_AZ</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Clearance_Hepatocyte_AZ</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Half_Life_Obach</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>PAINS_alert</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>BRENK_alert</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>NIH_alert</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>AMES</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ClinTox</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>DILI</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Carcinogens_Lagunin</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>hERG</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>CYP1A2_Veith</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2C19_Veith</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2C9_Veith</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2D6_Veith</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>CYP3A4_Veith</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>HIA_Hou</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Bioavailability_Ma</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>PAMPA_NCATS</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Pgp_Broccatelli</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Caco2_Wang</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>PPBR_AZ</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>VDss_Lombardo</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>molecular_weight</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>logP</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>QED</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Lipinski</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>sa_score</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>sa_accessibility</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>liability_alert_count</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>passes_qsar_uncertainty</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>passes_optimal</t>
         </is>
@@ -1179,119 +1413,369 @@
     <row r="2" ht="92" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)nc(N)c4)C3)C2)c1</t>
+          <t>CCCCC#Cc1cncc(N2CCC3(CN4COCOc5cc(N)c(cc53)C4=O)C2)c1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>0.6578947368421053</v>
+        <v>0.4961832061068702</v>
       </c>
       <c r="F2" s="3">
-        <v>11.42</v>
+        <v>11.22</v>
       </c>
       <c r="G2" s="3">
-        <v>0.5473052419692593</v>
-      </c>
-      <c r="H2" s="3">
-        <v>3.526186204162281</v>
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I2" s="3">
-        <v>5.452694758030741</v>
+        <v>0.547305243864102</v>
       </c>
       <c r="J2" s="3">
-        <v>2.925300000000001</v>
+        <v>3.52618621954716</v>
       </c>
       <c r="K2" s="3">
-        <v>-4.824358208606556</v>
+        <v>5.452694756135898</v>
       </c>
       <c r="L2" s="3">
-        <v>1.498448396736448E-05</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+        <v>1.190455835561637</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.498262021714247</v>
+      </c>
+      <c r="N2" s="3">
+        <v>30.01399425243151</v>
+      </c>
+      <c r="O2" s="3">
+        <v>35.71154865366999</v>
+      </c>
+      <c r="P2" s="3">
+        <v>4.809544164438363</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.498262021714247</v>
+      </c>
+      <c r="R2" s="3">
+        <v>1.636297523158871</v>
+      </c>
+      <c r="S2" s="3">
+        <v>146.909336778372</v>
+      </c>
+      <c r="T2" s="3">
+        <v>3.832950601878439</v>
+      </c>
+      <c r="U2" s="3">
+        <v>5.786137726998287</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.498262021714247</v>
+      </c>
+      <c r="W2" s="3">
+        <v>3.133400000000001</v>
+      </c>
+      <c r="X2" s="3">
+        <v>-5.07290291377595</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>8.454678277705419E-06</v>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N2" s="3">
-        <v>30.85870742797852</v>
-      </c>
-      <c r="O2" s="3">
-        <v>25.46169090270996</v>
-      </c>
-      <c r="P2" s="3">
-        <v>41.37262725830078</v>
-      </c>
-      <c r="Q2" s="3">
+      <c r="AA2" s="3">
+        <v>34.03657913208008</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>35.33199691772461</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>45.15724945068359</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>0.4128183424472809</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>0.317070335149765</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>0.8789542317390442</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>0.05042798444628716</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>0.8694758415222168</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>0.4486382901668549</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>0.7849494814872742</v>
+      </c>
+      <c r="AN2" s="3">
+        <v>0.8201218843460083</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>0.2035863697528839</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>0.9765839576721191</v>
+      </c>
+      <c r="AQ2" s="3">
+        <v>0.9999567866325378</v>
+      </c>
+      <c r="AR2" s="3">
+        <v>0.7418512105941772</v>
+      </c>
+      <c r="AS2" s="3">
+        <v>0.9514479637145996</v>
+      </c>
+      <c r="AT2" s="3">
+        <v>0.8597750663757324</v>
+      </c>
+      <c r="AU2" s="3">
+        <v>-4.779772758483887</v>
+      </c>
+      <c r="AV2" s="3">
+        <v>96.93354797363281</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>8.543520927429199</v>
+      </c>
+      <c r="AX2" s="3">
+        <v>432.5240000000002</v>
+      </c>
+      <c r="AY2" s="3">
+        <v>3.133400000000001</v>
+      </c>
+      <c r="AZ2" s="3">
+        <v>0.4560080622686213</v>
+      </c>
+      <c r="BA2" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB2" s="3">
+        <v>5.559767419573375</v>
+      </c>
+      <c r="BC2" s="3">
+        <v>0.4933591756029583</v>
+      </c>
+      <c r="BD2" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE2" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CCC3(CN4COCOc5cc(N)c(cc53)C4=O)C2)c1</t>
+          <t>CCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)nc(N)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>0.4961832061068702</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="F3" s="3">
-        <v>11.22</v>
+        <v>11.42</v>
       </c>
       <c r="G3" s="3">
-        <v>0.5473052419692593</v>
-      </c>
-      <c r="H3" s="3">
-        <v>3.526186204162281</v>
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I3" s="3">
-        <v>5.452694758030741</v>
+        <v>0.547305243864102</v>
       </c>
       <c r="J3" s="3">
-        <v>3.133400000000001</v>
+        <v>3.52618621954716</v>
       </c>
       <c r="K3" s="3">
-        <v>-5.07290291377595</v>
+        <v>5.452694756135898</v>
       </c>
       <c r="L3" s="3">
-        <v>8.454678277705419E-06</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+        <v>1.350973024854653</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.5990026861033019</v>
+      </c>
+      <c r="N3" s="3">
+        <v>55.68607920047454</v>
+      </c>
+      <c r="O3" s="3">
+        <v>73.79130591976713</v>
+      </c>
+      <c r="P3" s="3">
+        <v>4.649026975145347</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.5990026861033019</v>
+      </c>
+      <c r="R3" s="3">
+        <v>1.502891956451388</v>
+      </c>
+      <c r="S3" s="3">
+        <v>334.9795459883102</v>
+      </c>
+      <c r="T3" s="3">
+        <v>3.474981710382875</v>
+      </c>
+      <c r="U3" s="3">
+        <v>5.823072239907819</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.5990026861033019</v>
+      </c>
+      <c r="W3" s="3">
+        <v>2.925300000000001</v>
+      </c>
+      <c r="X3" s="3">
+        <v>-4.824358208606556</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>1.498448396736448E-05</v>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N3" s="3">
-        <v>34.03657913208008</v>
-      </c>
-      <c r="O3" s="3">
-        <v>35.33199691772461</v>
-      </c>
-      <c r="P3" s="3">
-        <v>45.15725326538086</v>
-      </c>
-      <c r="Q3" s="3">
+      <c r="AA3" s="3">
+        <v>30.85870742797852</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>25.46169090270996</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>41.37262725830078</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.2860892415046692</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>0.5141839981079102</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0.8790133595466614</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>0.04890316352248192</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>0.9000399708747864</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>0.07134749740362167</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>0.3509548604488373</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>0.5367151498794556</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>0.1045412197709084</v>
+      </c>
+      <c r="AP3" s="3">
+        <v>0.9280899167060852</v>
+      </c>
+      <c r="AQ3" s="3">
+        <v>0.999531090259552</v>
+      </c>
+      <c r="AR3" s="3">
+        <v>0.7743515372276306</v>
+      </c>
+      <c r="AS3" s="3">
+        <v>0.8736506700515747</v>
+      </c>
+      <c r="AT3" s="3">
+        <v>0.7783913612365723</v>
+      </c>
+      <c r="AU3" s="3">
+        <v>-5.082280158996582</v>
+      </c>
+      <c r="AV3" s="3">
+        <v>96.35707092285156</v>
+      </c>
+      <c r="AW3" s="3">
+        <v>9.466903686523438</v>
+      </c>
+      <c r="AX3" s="3">
+        <v>418.5450000000002</v>
+      </c>
+      <c r="AY3" s="3">
+        <v>2.925300000000001</v>
+      </c>
+      <c r="AZ3" s="3">
+        <v>0.5718515345864986</v>
+      </c>
+      <c r="BA3" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB3" s="3">
+        <v>3.522593138158119</v>
+      </c>
+      <c r="BC3" s="3">
+        <v>0.7197118735379868</v>
+      </c>
+      <c r="BD3" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="92" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1ccc(N2CCC3(CN(C(=O)c4cc5c(cc4N)OCO5)C3)C2)cn1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1303,163 +1787,538 @@
         <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>0.6115702479338843</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="F4" s="3">
-        <v>11.5</v>
+        <v>5.09</v>
       </c>
       <c r="G4" s="3">
-        <v>0.5576247392552036</v>
-      </c>
-      <c r="H4" s="3">
-        <v>3.610977141714381</v>
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I4" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J4" s="3">
-        <v>3.286700000000002</v>
+        <v>3.610977157306949</v>
       </c>
       <c r="K4" s="3">
-        <v>-5.183149985103853</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L4" s="3">
-        <v>6.559187033864976E-06</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+        <v>0.9332508602781384</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="N4" s="3">
+        <v>10.96066001159812</v>
+      </c>
+      <c r="O4" s="3">
+        <v>7.922061390836396</v>
+      </c>
+      <c r="P4" s="3">
+        <v>5.066749139721861</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="R4" s="3">
+        <v>2.189975866909783</v>
+      </c>
+      <c r="S4" s="3">
+        <v>33.57858503776772</v>
+      </c>
+      <c r="T4" s="3">
+        <v>4.473937608473038</v>
+      </c>
+      <c r="U4" s="3">
+        <v>5.659560670970686</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="W4" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="X4" s="3">
+        <v>-5.242372322098043</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>5.723051814844524E-06</v>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N4" s="3">
-        <v>62.00168609619141</v>
-      </c>
-      <c r="O4" s="3">
-        <v>58.01309204101562</v>
-      </c>
-      <c r="P4" s="3">
-        <v>53.0703010559082</v>
-      </c>
-      <c r="Q4" s="3">
+      <c r="AA4" s="3">
+        <v>54.03302001953125</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>51.58975219726562</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>46.11929321289062</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>0.1514938920736313</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>0.3794129490852356</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0.790505588054657</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>0.05281468108296394</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>0.8946078419685364</v>
+      </c>
+      <c r="AL4" s="3">
+        <v>0.4100111424922943</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>0.6163968443870544</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>0.7340325713157654</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>0.2590197920799255</v>
+      </c>
+      <c r="AP4" s="3">
+        <v>0.9837436676025391</v>
+      </c>
+      <c r="AQ4" s="3">
+        <v>0.9999759793281555</v>
+      </c>
+      <c r="AR4" s="3">
+        <v>0.7540546655654907</v>
+      </c>
+      <c r="AS4" s="3">
+        <v>0.9556649327278137</v>
+      </c>
+      <c r="AT4" s="3">
+        <v>0.8375112414360046</v>
+      </c>
+      <c r="AU4" s="3">
+        <v>-4.578262329101562</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>98.41603851318359</v>
+      </c>
+      <c r="AW4" s="3">
+        <v>6.461910247802734</v>
+      </c>
+      <c r="AX4" s="3">
+        <v>421.4720000000002</v>
+      </c>
+      <c r="AY4" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="AZ4" s="3">
+        <v>0.7109076812540762</v>
+      </c>
+      <c r="BA4" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="3">
+        <v>3.5375694365788</v>
+      </c>
+      <c r="BC4" s="3">
+        <v>0.7180478403801334</v>
+      </c>
+      <c r="BD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CNc1cc(CN2CC3(CCN(c4cncc(C#CCO)c4)C3)C2)cc(C(F)(F)F)c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([18F])c5c(c4)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>0.5</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="F5" s="3">
-        <v>10.23</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G5" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H5" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I5" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J5" s="3">
-        <v>3.198200000000002</v>
+        <v>3.610977157306949</v>
       </c>
       <c r="K5" s="3">
-        <v>-5.109109607233802</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L5" s="3">
-        <v>7.778402149652514E-06</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+        <v>0.9332508602781384</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="N5" s="3">
+        <v>10.96066001159812</v>
+      </c>
+      <c r="O5" s="3">
+        <v>7.922061390836396</v>
+      </c>
+      <c r="P5" s="3">
+        <v>5.066749139721861</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="R5" s="3">
+        <v>2.189975866909783</v>
+      </c>
+      <c r="S5" s="3">
+        <v>33.57858503776772</v>
+      </c>
+      <c r="T5" s="3">
+        <v>4.473937608473038</v>
+      </c>
+      <c r="U5" s="3">
+        <v>5.659560670970686</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0.3024548628820531</v>
+      </c>
+      <c r="W5" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="X5" s="3">
+        <v>-5.235777868917642</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>5.810615403983823E-06</v>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N5" s="3">
-        <v>10.30675029754639</v>
-      </c>
-      <c r="O5" s="3">
-        <v>4.953836917877197</v>
-      </c>
-      <c r="P5" s="3">
-        <v>63.28201293945312</v>
-      </c>
-      <c r="Q5" s="3">
+      <c r="AA5" s="3">
+        <v>54.02364349365234</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>51.60739898681641</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>46.01803207397461</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>0.1515597552061081</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>0.3794240057468414</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>0.7904849052429199</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>0.0527871735394001</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>0.8945648074150085</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>0.4096334874629974</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>0.6159687638282776</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>0.7336847186088562</v>
+      </c>
+      <c r="AO5" s="3">
+        <v>0.2587461173534393</v>
+      </c>
+      <c r="AP5" s="3">
+        <v>0.9837337732315063</v>
+      </c>
+      <c r="AQ5" s="3">
+        <v>0.9999759793281555</v>
+      </c>
+      <c r="AR5" s="3">
+        <v>0.7541525363922119</v>
+      </c>
+      <c r="AS5" s="3">
+        <v>0.955665111541748</v>
+      </c>
+      <c r="AT5" s="3">
+        <v>0.8373624086380005</v>
+      </c>
+      <c r="AU5" s="3">
+        <v>-4.578091621398926</v>
+      </c>
+      <c r="AV5" s="3">
+        <v>98.40773010253906</v>
+      </c>
+      <c r="AW5" s="3">
+        <v>6.452359199523926</v>
+      </c>
+      <c r="AX5" s="3">
+        <v>420.4749380000002</v>
+      </c>
+      <c r="AY5" s="3">
+        <v>3.453500000000002</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>0.7122693165783467</v>
+      </c>
+      <c r="BA5" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB5" s="3">
+        <v>3.5375694365788</v>
+      </c>
+      <c r="BC5" s="3">
+        <v>0.7180478403801334</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE5" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="92" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)c1</t>
+          <t>CNc1cc(CN2CC3(CCN(c4cncc(C#CCO)c4)C3)C2)cc(C(F)(F)F)c1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>0.6271186440677966</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="3">
-        <v>5.09</v>
+        <v>10.23</v>
       </c>
       <c r="G6" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I6" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J6" s="3">
-        <v>3.453500000000002</v>
+        <v>3.610977157306949</v>
       </c>
       <c r="K6" s="3">
-        <v>-5.242372322098043</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L6" s="3">
-        <v>5.723051814844524E-06</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+        <v>1.113436676863066</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.4498076455120736</v>
+      </c>
+      <c r="N6" s="3">
+        <v>20.90991817294041</v>
+      </c>
+      <c r="O6" s="3">
+        <v>18.73563396946918</v>
+      </c>
+      <c r="P6" s="3">
+        <v>4.886563323136934</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.4498076455120736</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1.705350652306338</v>
+      </c>
+      <c r="S6" s="3">
+        <v>98.86889084296909</v>
+      </c>
+      <c r="T6" s="3">
+        <v>4.004940337933269</v>
+      </c>
+      <c r="U6" s="3">
+        <v>5.768186308340598</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0.4498076455120736</v>
+      </c>
+      <c r="W6" s="3">
+        <v>3.198200000000002</v>
+      </c>
+      <c r="X6" s="3">
+        <v>-5.109109607233802</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>7.778402149652514E-06</v>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N6" s="3">
-        <v>54.03302001953125</v>
-      </c>
-      <c r="O6" s="3">
-        <v>51.58975219726562</v>
-      </c>
-      <c r="P6" s="3">
-        <v>46.11928939819336</v>
-      </c>
-      <c r="Q6" s="3">
+      <c r="AA6" s="3">
+        <v>10.30675029754639</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>4.953838348388672</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>63.28201293945312</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>0.172451987862587</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>0.6441282033920288</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>0.6298868656158447</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>0.09360764920711517</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>0.9688534736633301</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>0.2428222149610519</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>0.2800058722496033</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>0.3691545128822327</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0.5387910604476929</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>0.9079670906066895</v>
+      </c>
+      <c r="AQ6" s="3">
+        <v>0.9994224309921265</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>0.8015594482421875</v>
+      </c>
+      <c r="AS6" s="3">
+        <v>0.8959123492240906</v>
+      </c>
+      <c r="AT6" s="3">
+        <v>0.8629838824272156</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>-5.264070510864258</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>90.62617492675781</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>15.84818458557129</v>
+      </c>
+      <c r="AX6" s="3">
+        <v>430.4740000000002</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>3.198200000000002</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>0.7301132337038804</v>
+      </c>
+      <c r="BA6" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>3.496978657810881</v>
+      </c>
+      <c r="BC6" s="3">
+        <v>0.7225579269099021</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4N)OCO5)C3)C2)c1</t>
+          <t>CCCCC#Cc1ccc(N2CCC3(CN(C(=O)c4cc5c(cc4N)OCO5)C3)C2)cn1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1471,51 +2330,176 @@
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>0.7727272727272727</v>
+        <v>0.6115702479338843</v>
       </c>
       <c r="F7" s="3">
-        <v>5.37</v>
+        <v>11.5</v>
       </c>
       <c r="G7" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H7" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I7" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305315</v>
       </c>
       <c r="J7" s="3">
-        <v>3.286700000000001</v>
+        <v>3.610977157306949</v>
       </c>
       <c r="K7" s="3">
-        <v>-5.183149985103852</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L7" s="3">
-        <v>6.559187033864989E-06</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+        <v>1.285191299073669</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.5885768164687759</v>
+      </c>
+      <c r="N7" s="3">
+        <v>51.08388057955189</v>
+      </c>
+      <c r="O7" s="3">
+        <v>74.84643175913052</v>
+      </c>
+      <c r="P7" s="3">
+        <v>4.714808700926332</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.5885768164687759</v>
+      </c>
+      <c r="R7" s="3">
+        <v>1.353881764653936</v>
+      </c>
+      <c r="S7" s="3">
+        <v>274.6640751631294</v>
+      </c>
+      <c r="T7" s="3">
+        <v>3.561198140647531</v>
+      </c>
+      <c r="U7" s="3">
+        <v>5.868419261205132</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0.5885768164687759</v>
+      </c>
+      <c r="W7" s="3">
+        <v>3.286700000000002</v>
+      </c>
+      <c r="X7" s="3">
+        <v>-5.183149985103853</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>6.559187033864976E-06</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N7" s="3">
-        <v>59.47089767456055</v>
-      </c>
-      <c r="O7" s="3">
-        <v>57.21721267700195</v>
-      </c>
-      <c r="P7" s="3">
-        <v>40.80253219604492</v>
-      </c>
-      <c r="Q7" s="3">
+      <c r="AA7" s="3">
+        <v>62.00168609619141</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>58.01309204101562</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>53.0703010559082</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0.3010247945785522</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0.3763807415962219</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0.85511714220047</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0.07315777242183685</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>0.8861689567565918</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0.2670863270759583</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>0.620905339717865</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0.7570825815200806</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0.1881253570318222</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>0.9700537919998169</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>0.9998720288276672</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>0.743526816368103</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>0.9412748217582703</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>0.8953615427017212</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>-4.690360069274902</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>101.8853302001953</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>6.763211250305176</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>432.5240000000002</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>3.286700000000002</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>0.4537042148229764</v>
+      </c>
+      <c r="BA7" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>3.47502284007115</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>0.7249974622143167</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="92" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([18F])c5c(c4)OCO5)C3)C2)c1</t>
+          <t>CCCC#Cc1ccc(N2CCC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)cn1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1527,44 +2511,169 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>0.6271186440677966</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="F8" s="3">
-        <v>9.630000000000001</v>
+        <v>11.47</v>
       </c>
       <c r="G8" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I8" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J8" s="3">
-        <v>3.453500000000002</v>
+        <v>3.61097715730695</v>
       </c>
       <c r="K8" s="3">
-        <v>-5.235777868917642</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L8" s="3">
-        <v>5.810615403983823E-06</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+        <v>1.004771354099617</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.3347623126543536</v>
+      </c>
+      <c r="N8" s="3">
+        <v>13.13000513882993</v>
+      </c>
+      <c r="O8" s="3">
+        <v>8.363187868173434</v>
+      </c>
+      <c r="P8" s="3">
+        <v>4.995228645900383</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.3347623126543536</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2.231707234599007</v>
+      </c>
+      <c r="S8" s="3">
+        <v>45.80421946864273</v>
+      </c>
+      <c r="T8" s="3">
+        <v>4.33909451309785</v>
+      </c>
+      <c r="U8" s="3">
+        <v>5.651362778702916</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.3347623126543536</v>
+      </c>
+      <c r="W8" s="3">
+        <v>3.453500000000003</v>
+      </c>
+      <c r="X8" s="3">
+        <v>-5.242372322098045</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>5.723051814844501E-06</v>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N8" s="3">
-        <v>54.02364349365234</v>
-      </c>
-      <c r="O8" s="3">
-        <v>51.60739898681641</v>
-      </c>
-      <c r="P8" s="3">
-        <v>46.01803207397461</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="AA8" s="3">
+        <v>57.12314987182617</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>53.15890502929688</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>59.37638473510742</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0.2634467482566833</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0.3268089890480042</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0.8230131864547729</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>0.09272345155477524</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0.7996328473091125</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>0.3018380403518677</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>0.4526433348655701</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>0.5517083406448364</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0.1512510031461716</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>0.9123425483703613</v>
+      </c>
+      <c r="AQ8" s="3">
+        <v>0.9997068643569946</v>
+      </c>
+      <c r="AR8" s="3">
+        <v>0.7845497727394104</v>
+      </c>
+      <c r="AS8" s="3">
+        <v>0.9428170919418335</v>
+      </c>
+      <c r="AT8" s="3">
+        <v>0.8034658432006836</v>
+      </c>
+      <c r="AU8" s="3">
+        <v>-4.516212463378906</v>
+      </c>
+      <c r="AV8" s="3">
+        <v>98.88426971435547</v>
+      </c>
+      <c r="AW8" s="3">
+        <v>7.63823413848877</v>
+      </c>
+      <c r="AX8" s="3">
+        <v>421.4720000000002</v>
+      </c>
+      <c r="AY8" s="3">
+        <v>3.453500000000003</v>
+      </c>
+      <c r="AZ8" s="3">
+        <v>0.7109076812540762</v>
+      </c>
+      <c r="BA8" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB8" s="3">
+        <v>3.530366325083554</v>
+      </c>
+      <c r="BC8" s="3">
+        <v>0.7188481861018274</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1589,45 +2698,170 @@
         <v>10.97</v>
       </c>
       <c r="G9" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I9" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J9" s="3">
+        <v>3.61097715730695</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5.442375258869468</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1.25207912233329</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0.5958091510126513</v>
+      </c>
+      <c r="N9" s="3">
+        <v>49.88070890814073</v>
+      </c>
+      <c r="O9" s="3">
+        <v>75.34879473122852</v>
+      </c>
+      <c r="P9" s="3">
+        <v>4.747920877666711</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.5958091510126513</v>
+      </c>
+      <c r="R9" s="3">
+        <v>1.214208269474237</v>
+      </c>
+      <c r="S9" s="3">
+        <v>262.9450855906345</v>
+      </c>
+      <c r="T9" s="3">
+        <v>3.580134941681914</v>
+      </c>
+      <c r="U9" s="3">
+        <v>5.915706813651507</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0.5958091510126513</v>
+      </c>
+      <c r="W9" s="3">
         <v>3.422880000000002</v>
       </c>
-      <c r="K9" s="3">
+      <c r="X9" s="3">
         <v>-5.34886473594606</v>
       </c>
-      <c r="L9" s="3">
+      <c r="Y9" s="3">
         <v>4.478527693339253E-06</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N9" s="3">
+      <c r="AA9" s="3">
         <v>50.9268913269043</v>
       </c>
-      <c r="O9" s="3">
+      <c r="AB9" s="3">
         <v>50.9757194519043</v>
       </c>
-      <c r="P9" s="3">
+      <c r="AC9" s="3">
         <v>40.63362884521484</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="AD9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0.2754431366920471</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>0.2086796313524246</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0.9090962409973145</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>0.06169123575091362</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>0.7485303282737732</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>0.2723854780197144</v>
+      </c>
+      <c r="AM9" s="3">
+        <v>0.656551718711853</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>0.7990891337394714</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>0.1086594834923744</v>
+      </c>
+      <c r="AP9" s="3">
+        <v>0.9628103375434875</v>
+      </c>
+      <c r="AQ9" s="3">
+        <v>0.9999311566352844</v>
+      </c>
+      <c r="AR9" s="3">
+        <v>0.7291480302810669</v>
+      </c>
+      <c r="AS9" s="3">
+        <v>0.9398983120918274</v>
+      </c>
+      <c r="AT9" s="3">
+        <v>0.8420951962471008</v>
+      </c>
+      <c r="AU9" s="3">
+        <v>-4.587052822113037</v>
+      </c>
+      <c r="AV9" s="3">
+        <v>98.45797729492188</v>
+      </c>
+      <c r="AW9" s="3">
+        <v>5.001123428344727</v>
+      </c>
+      <c r="AX9" s="3">
+        <v>442.5190000000002</v>
+      </c>
+      <c r="AY9" s="3">
+        <v>3.422880000000002</v>
+      </c>
+      <c r="AZ9" s="3">
+        <v>0.5354297161641219</v>
+      </c>
+      <c r="BA9" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB9" s="3">
+        <v>5.607484765379528</v>
+      </c>
+      <c r="BC9" s="3">
+        <v>0.4880572482911636</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="92" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1ccc(N2CCC3(CN(C(=O)c4cc(F)c5c(c4)OCO5)C3)C2)cn1</t>
+          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4N)OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1639,51 +2873,176 @@
         <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>0.4883720930232558</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="F10" s="3">
-        <v>11.47</v>
+        <v>5.37</v>
       </c>
       <c r="G10" s="3">
-        <v>0.5576247392552037</v>
-      </c>
-      <c r="H10" s="3">
-        <v>3.610977141714382</v>
+        <v>5</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I10" s="3">
-        <v>5.442375260744797</v>
+        <v>0.5576247411305316</v>
       </c>
       <c r="J10" s="3">
-        <v>3.453500000000003</v>
+        <v>3.61097715730695</v>
       </c>
       <c r="K10" s="3">
-        <v>-5.242372322098045</v>
+        <v>5.442375258869468</v>
       </c>
       <c r="L10" s="3">
-        <v>5.723051814844501E-06</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+        <v>1.202643999226805</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.6027867767415637</v>
+      </c>
+      <c r="N10" s="3">
+        <v>48.16748725694215</v>
+      </c>
+      <c r="O10" s="3">
+        <v>76.0808612751983</v>
+      </c>
+      <c r="P10" s="3">
+        <v>4.797356000773195</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.6027867767415637</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1.049982151963999</v>
+      </c>
+      <c r="S10" s="3">
+        <v>242.1620484371657</v>
+      </c>
+      <c r="T10" s="3">
+        <v>3.61589391835973</v>
+      </c>
+      <c r="U10" s="3">
+        <v>5.97881808318666</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0.6027867767415637</v>
+      </c>
+      <c r="W10" s="3">
+        <v>3.286700000000001</v>
+      </c>
+      <c r="X10" s="3">
+        <v>-5.183149985103852</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>6.559187033864989E-06</v>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N10" s="3">
-        <v>57.1231575012207</v>
-      </c>
-      <c r="O10" s="3">
-        <v>53.15890502929688</v>
-      </c>
-      <c r="P10" s="3">
-        <v>59.37638473510742</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="AA10" s="3">
+        <v>59.47089767456055</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>57.21721267700195</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>40.80253219604492</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0.1844686567783356</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0.420243501663208</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0.8358315229415894</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>0.04515016451478004</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>0.9386307001113892</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>0.4181108474731445</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>0.7442826628684998</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>0.8617993593215942</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>0.2975648641586304</v>
+      </c>
+      <c r="AP10" s="3">
+        <v>0.9936869740486145</v>
+      </c>
+      <c r="AQ10" s="3">
+        <v>0.9999872446060181</v>
+      </c>
+      <c r="AR10" s="3">
+        <v>0.7217900156974792</v>
+      </c>
+      <c r="AS10" s="3">
+        <v>0.9570225477218628</v>
+      </c>
+      <c r="AT10" s="3">
+        <v>0.9055355191230774</v>
+      </c>
+      <c r="AU10" s="3">
+        <v>-4.767285823822021</v>
+      </c>
+      <c r="AV10" s="3">
+        <v>101.1879043579102</v>
+      </c>
+      <c r="AW10" s="3">
+        <v>5.748510837554932</v>
+      </c>
+      <c r="AX10" s="3">
+        <v>432.5240000000002</v>
+      </c>
+      <c r="AY10" s="3">
+        <v>3.286700000000001</v>
+      </c>
+      <c r="AZ10" s="3">
+        <v>0.4537042148229764</v>
+      </c>
+      <c r="BA10" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB10" s="3">
+        <v>3.481991067495898</v>
+      </c>
+      <c r="BC10" s="3">
+        <v>0.724223214722678</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="92" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N(C)C)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1695,51 +3054,176 @@
         <v>1</v>
       </c>
       <c r="E11" s="3">
-        <v>0.6460176991150443</v>
+        <v>0.5798319327731093</v>
       </c>
       <c r="F11" s="3">
-        <v>5.42</v>
+        <v>11.57</v>
       </c>
       <c r="G11" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H11" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I11" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J11" s="3">
-        <v>3.140200000000001</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K11" s="3">
-        <v>-4.893387986062748</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L11" s="3">
-        <v>1.278238852491739E-05</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+        <v>1.350083032418545</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.5538972903245317</v>
+      </c>
+      <c r="N11" s="3">
+        <v>52.85744973393292</v>
+      </c>
+      <c r="O11" s="3">
+        <v>73.97049186169482</v>
+      </c>
+      <c r="P11" s="3">
+        <v>4.649916967581455</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.5538972903245317</v>
+      </c>
+      <c r="R11" s="3">
+        <v>1.838418337923174</v>
+      </c>
+      <c r="S11" s="3">
+        <v>272.7229723024533</v>
+      </c>
+      <c r="T11" s="3">
+        <v>3.564278278545373</v>
+      </c>
+      <c r="U11" s="3">
+        <v>5.735555656617537</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.5538972903245317</v>
+      </c>
+      <c r="W11" s="3">
+        <v>3.233900000000002</v>
+      </c>
+      <c r="X11" s="3">
+        <v>-5.050155817708335</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>8.909312293304308E-06</v>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N11" s="3">
-        <v>22.13141822814941</v>
-      </c>
-      <c r="O11" s="3">
-        <v>26.04515075683594</v>
-      </c>
-      <c r="P11" s="3">
-        <v>48.23393630981445</v>
-      </c>
-      <c r="Q11" s="3">
+      <c r="AA11" s="3">
+        <v>39.75580978393555</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>32.81678771972656</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>42.63827133178711</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0.3349597156047821</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>0.4971658289432526</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0.8305774927139282</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>0.05206185579299927</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>0.9213895797729492</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>0.2205078303813934</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>0.4619075357913971</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>0.5620790719985962</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>0.1509415060281754</v>
+      </c>
+      <c r="AP11" s="3">
+        <v>0.957487940788269</v>
+      </c>
+      <c r="AQ11" s="3">
+        <v>0.9998504519462585</v>
+      </c>
+      <c r="AR11" s="3">
+        <v>0.8074136972427368</v>
+      </c>
+      <c r="AS11" s="3">
+        <v>0.9490911364555359</v>
+      </c>
+      <c r="AT11" s="3">
+        <v>0.8077398538589478</v>
+      </c>
+      <c r="AU11" s="3">
+        <v>-4.965895175933838</v>
+      </c>
+      <c r="AV11" s="3">
+        <v>95.56562805175781</v>
+      </c>
+      <c r="AW11" s="3">
+        <v>10.71188068389893</v>
+      </c>
+      <c r="AX11" s="3">
+        <v>417.5570000000001</v>
+      </c>
+      <c r="AY11" s="3">
+        <v>3.233900000000002</v>
+      </c>
+      <c r="AZ11" s="3">
+        <v>0.6111796571419246</v>
+      </c>
+      <c r="BA11" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB11" s="3">
+        <v>3.50520040847401</v>
+      </c>
+      <c r="BC11" s="3">
+        <v>0.7216443990584434</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE11" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="92" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CCC(C#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1)CC</t>
+          <t>CC(C)CC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1751,51 +3235,176 @@
         <v>1</v>
       </c>
       <c r="E12" s="3">
-        <v>0.5161290322580645</v>
+        <v>0.5289256198347108</v>
       </c>
       <c r="F12" s="3">
-        <v>7.47</v>
+        <v>8.57</v>
       </c>
       <c r="G12" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H12" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I12" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J12" s="3">
-        <v>3.386200000000002</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K12" s="3">
-        <v>-5.163112760649856</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L12" s="3">
-        <v>6.868900720401043E-06</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
+        <v>1.332427676584167</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.5611803271318311</v>
+      </c>
+      <c r="N12" s="3">
+        <v>52.31606860382773</v>
+      </c>
+      <c r="O12" s="3">
+        <v>74.25133344613076</v>
+      </c>
+      <c r="P12" s="3">
+        <v>4.667572323415833</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.5611803271318311</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1.70810370776367</v>
+      </c>
+      <c r="S12" s="3">
+        <v>270.6083029741987</v>
+      </c>
+      <c r="T12" s="3">
+        <v>3.567658882237444</v>
+      </c>
+      <c r="U12" s="3">
+        <v>5.767485764594221</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0.5611803271318311</v>
+      </c>
+      <c r="W12" s="3">
+        <v>2.996100000000001</v>
+      </c>
+      <c r="X12" s="3">
+        <v>-4.789964315096382</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>1.621943362959058E-05</v>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N12" s="3">
-        <v>24.38673973083496</v>
-      </c>
-      <c r="O12" s="3">
-        <v>22.29123878479004</v>
-      </c>
-      <c r="P12" s="3">
-        <v>54.57378005981445</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="AA12" s="3">
+        <v>24.80001449584961</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>23.34781265258789</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>43.05011367797852</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0.3229777216911316</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>0.4890483915805817</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>0.8431566953659058</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>0.04133586958050728</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>0.8974877595901489</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>0.08953447639942169</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>0.3851622939109802</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>0.4774286150932312</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>0.1085920929908752</v>
+      </c>
+      <c r="AP12" s="3">
+        <v>0.9089075326919556</v>
+      </c>
+      <c r="AQ12" s="3">
+        <v>0.9997041821479797</v>
+      </c>
+      <c r="AR12" s="3">
+        <v>0.7743037939071655</v>
+      </c>
+      <c r="AS12" s="3">
+        <v>0.8871881365776062</v>
+      </c>
+      <c r="AT12" s="3">
+        <v>0.6713687181472778</v>
+      </c>
+      <c r="AU12" s="3">
+        <v>-5.05207347869873</v>
+      </c>
+      <c r="AV12" s="3">
+        <v>93.55834197998047</v>
+      </c>
+      <c r="AW12" s="3">
+        <v>10.05699634552002</v>
+      </c>
+      <c r="AX12" s="3">
+        <v>403.5300000000001</v>
+      </c>
+      <c r="AY12" s="3">
+        <v>2.996100000000001</v>
+      </c>
+      <c r="AZ12" s="3">
+        <v>0.6075338398766694</v>
+      </c>
+      <c r="BA12" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB12" s="3">
+        <v>3.522390839921285</v>
+      </c>
+      <c r="BC12" s="3">
+        <v>0.7197343511198573</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="92" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CC(C)CC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1</t>
+          <t>CCCCC#Cc1ccc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)cn1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1807,51 +3416,176 @@
         <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>0.5289256198347108</v>
+        <v>0.5</v>
       </c>
       <c r="F13" s="3">
-        <v>8.57</v>
+        <v>11.48</v>
       </c>
       <c r="G13" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H13" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I13" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J13" s="3">
-        <v>2.996100000000001</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K13" s="3">
-        <v>-4.789964315096382</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L13" s="3">
-        <v>1.621943362959058E-05</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+        <v>1.348666686647993</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.5683451305523907</v>
+      </c>
+      <c r="N13" s="3">
+        <v>53.57571271843081</v>
+      </c>
+      <c r="O13" s="3">
+        <v>73.85775898168853</v>
+      </c>
+      <c r="P13" s="3">
+        <v>4.651333313352007</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.5683451305523907</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1.716762549513675</v>
+      </c>
+      <c r="S13" s="3">
+        <v>290.1503792311362</v>
+      </c>
+      <c r="T13" s="3">
+        <v>3.537376857469321</v>
+      </c>
+      <c r="U13" s="3">
+        <v>5.765289769234693</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.5683451305523907</v>
+      </c>
+      <c r="W13" s="3">
+        <v>3.140200000000001</v>
+      </c>
+      <c r="X13" s="3">
+        <v>-4.893387986062748</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>1.278238852491739E-05</v>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N13" s="3">
-        <v>24.80001449584961</v>
-      </c>
-      <c r="O13" s="3">
-        <v>23.34781455993652</v>
-      </c>
-      <c r="P13" s="3">
-        <v>43.05011367797852</v>
-      </c>
-      <c r="Q13" s="3">
+      <c r="AA13" s="3">
+        <v>20.17489242553711</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>23.7639102935791</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>56.34565353393555</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0.4605282247066498</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0.4387226998806</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0.8704509735107422</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0.05935602262616158</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0.8431379199028015</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0.1032470613718033</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0.3283776640892029</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0.442185640335083</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0.0779731422662735</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0.8376519083976746</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0.9987085461616516</v>
+      </c>
+      <c r="AR13" s="3">
+        <v>0.7852612137794495</v>
+      </c>
+      <c r="AS13" s="3">
+        <v>0.8799749612808228</v>
+      </c>
+      <c r="AT13" s="3">
+        <v>0.7288599014282227</v>
+      </c>
+      <c r="AU13" s="3">
+        <v>-4.895804405212402</v>
+      </c>
+      <c r="AV13" s="3">
+        <v>96.39573669433594</v>
+      </c>
+      <c r="AW13" s="3">
+        <v>11.46587753295898</v>
+      </c>
+      <c r="AX13" s="3">
+        <v>403.5300000000001</v>
+      </c>
+      <c r="AY13" s="3">
+        <v>3.140200000000001</v>
+      </c>
+      <c r="AZ13" s="3">
+        <v>0.4651159294127719</v>
+      </c>
+      <c r="BA13" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="3">
+        <v>3.437653483748047</v>
+      </c>
+      <c r="BC13" s="3">
+        <v>0.7291496129168837</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="92" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CC(C)CCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1</t>
+          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1863,51 +3597,176 @@
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>0.5537190082644629</v>
+        <v>0.6460176991150443</v>
       </c>
       <c r="F14" s="3">
-        <v>9.91</v>
+        <v>5.42</v>
       </c>
       <c r="G14" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H14" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I14" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J14" s="3">
-        <v>3.386200000000001</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K14" s="3">
-        <v>-5.163112760649854</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L14" s="3">
-        <v>6.868900720401071E-06</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+        <v>1.272993523563218</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.5854961462969426</v>
+      </c>
+      <c r="N14" s="3">
+        <v>50.48420689620324</v>
+      </c>
+      <c r="O14" s="3">
+        <v>75.08748585259288</v>
+      </c>
+      <c r="P14" s="3">
+        <v>4.727006476436783</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.5854961462969426</v>
+      </c>
+      <c r="R14" s="3">
+        <v>1.334814995148271</v>
+      </c>
+      <c r="S14" s="3">
+        <v>263.3697977917691</v>
+      </c>
+      <c r="T14" s="3">
+        <v>3.579434029694775</v>
+      </c>
+      <c r="U14" s="3">
+        <v>5.87457892317879</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0.5854961462969426</v>
+      </c>
+      <c r="W14" s="3">
+        <v>3.140200000000001</v>
+      </c>
+      <c r="X14" s="3">
+        <v>-4.893387986062748</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1.278238852491739E-05</v>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N14" s="3">
-        <v>29.61392211914062</v>
-      </c>
-      <c r="O14" s="3">
-        <v>28.70643997192383</v>
-      </c>
-      <c r="P14" s="3">
-        <v>54.54449462890625</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="AA14" s="3">
+        <v>22.13141822814941</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>26.04515075683594</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>48.23393630981445</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0.3091988861560822</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0.4710089564323425</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0.8624054193496704</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0.03987503796815872</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0.9063378572463989</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0.1281423568725586</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0.429051548242569</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0.5838853120803833</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0.1096794605255127</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0.9557859301567078</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0.9998464584350586</v>
+      </c>
+      <c r="AR14" s="3">
+        <v>0.7801386713981628</v>
+      </c>
+      <c r="AS14" s="3">
+        <v>0.9159609079360962</v>
+      </c>
+      <c r="AT14" s="3">
+        <v>0.7508474588394165</v>
+      </c>
+      <c r="AU14" s="3">
+        <v>-5.046236991882324</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>94.6217041015625</v>
+      </c>
+      <c r="AW14" s="3">
+        <v>10.82663440704346</v>
+      </c>
+      <c r="AX14" s="3">
+        <v>403.5300000000001</v>
+      </c>
+      <c r="AY14" s="3">
+        <v>3.140200000000001</v>
+      </c>
+      <c r="AZ14" s="3">
+        <v>0.4651159294127719</v>
+      </c>
+      <c r="BA14" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB14" s="3">
+        <v>3.445195565196011</v>
+      </c>
+      <c r="BC14" s="3">
+        <v>0.7283116038671099</v>
+      </c>
+      <c r="BD14" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="92" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1ccc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)cn1</t>
+          <t>CC(C)CCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1919,51 +3778,176 @@
         <v>1</v>
       </c>
       <c r="E15" s="3">
-        <v>0.5</v>
+        <v>0.5537190082644629</v>
       </c>
       <c r="F15" s="3">
-        <v>11.48</v>
+        <v>9.91</v>
       </c>
       <c r="G15" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I15" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J15" s="3">
-        <v>3.140200000000001</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K15" s="3">
-        <v>-4.893387986062748</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L15" s="3">
-        <v>1.278238852491739E-05</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+        <v>1.284913747638275</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.5897994585461864</v>
+      </c>
+      <c r="N15" s="3">
+        <v>51.26184942865336</v>
+      </c>
+      <c r="O15" s="3">
+        <v>74.83128343239022</v>
+      </c>
+      <c r="P15" s="3">
+        <v>4.715086252361725</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.5897994585461864</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.345571589696887</v>
+      </c>
+      <c r="S15" s="3">
+        <v>276.007374802656</v>
+      </c>
+      <c r="T15" s="3">
+        <v>3.559079313611199</v>
+      </c>
+      <c r="U15" s="3">
+        <v>5.87109319111225</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0.5897994585461864</v>
+      </c>
+      <c r="W15" s="3">
+        <v>3.386200000000001</v>
+      </c>
+      <c r="X15" s="3">
+        <v>-5.163112760649854</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>6.868900720401071E-06</v>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N15" s="3">
-        <v>20.17489242553711</v>
-      </c>
-      <c r="O15" s="3">
-        <v>23.7639102935791</v>
-      </c>
-      <c r="P15" s="3">
-        <v>56.34565353393555</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="AA15" s="3">
+        <v>29.61392211914062</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>28.70643997192383</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>54.54449462890625</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0.290806919336319</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0.5101267099380493</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0.8653945922851562</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0.04396987706422806</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0.9301586151123047</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0.09436273574829102</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0.4396128058433533</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0.589055597782135</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0.1086192578077316</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0.9567853808403015</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0.9997827410697937</v>
+      </c>
+      <c r="AR15" s="3">
+        <v>0.7906284332275391</v>
+      </c>
+      <c r="AS15" s="3">
+        <v>0.9222062826156616</v>
+      </c>
+      <c r="AT15" s="3">
+        <v>0.8188015222549438</v>
+      </c>
+      <c r="AU15" s="3">
+        <v>-5.051095962524414</v>
+      </c>
+      <c r="AV15" s="3">
+        <v>96.21928405761719</v>
+      </c>
+      <c r="AW15" s="3">
+        <v>12.13404369354248</v>
+      </c>
+      <c r="AX15" s="3">
+        <v>417.5570000000002</v>
+      </c>
+      <c r="AY15" s="3">
+        <v>3.386200000000001</v>
+      </c>
+      <c r="AZ15" s="3">
+        <v>0.5880519362749713</v>
+      </c>
+      <c r="BA15" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB15" s="3">
+        <v>3.543500143222021</v>
+      </c>
+      <c r="BC15" s="3">
+        <v>0.717388872975331</v>
+      </c>
+      <c r="BD15" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="92" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N(C)C)c4)C3)C2)c1</t>
+          <t>CCC(C#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc(N)c4)C3)C2)c1)CC</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1975,44 +3959,169 @@
         <v>1</v>
       </c>
       <c r="E16" s="3">
-        <v>0.5798319327731093</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F16" s="3">
-        <v>11.57</v>
+        <v>7.47</v>
       </c>
       <c r="G16" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H16" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I16" s="3">
-        <v>5.394846104919416</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J16" s="3">
-        <v>3.233900000000002</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K16" s="3">
-        <v>-5.050155817708335</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L16" s="3">
-        <v>8.909312293304308E-06</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
+        <v>1.290237119454657</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.5902141860166523</v>
+      </c>
+      <c r="N16" s="3">
+        <v>51.52935574146495</v>
+      </c>
+      <c r="O16" s="3">
+        <v>74.72757378714228</v>
+      </c>
+      <c r="P16" s="3">
+        <v>4.709762880545343</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.5902141860166523</v>
+      </c>
+      <c r="R16" s="3">
+        <v>1.359619281316019</v>
+      </c>
+      <c r="S16" s="3">
+        <v>279.9348213053364</v>
+      </c>
+      <c r="T16" s="3">
+        <v>3.552943075952705</v>
+      </c>
+      <c r="U16" s="3">
+        <v>5.866582685137981</v>
+      </c>
+      <c r="V16" s="3">
+        <v>0.5902141860166523</v>
+      </c>
+      <c r="W16" s="3">
+        <v>3.386200000000002</v>
+      </c>
+      <c r="X16" s="3">
+        <v>-5.163112760649856</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>6.868900720401043E-06</v>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N16" s="3">
-        <v>39.75580978393555</v>
-      </c>
-      <c r="O16" s="3">
-        <v>32.81678771972656</v>
-      </c>
-      <c r="P16" s="3">
-        <v>42.63827133178711</v>
-      </c>
-      <c r="Q16" s="3">
+      <c r="AA16" s="3">
+        <v>24.38673973083496</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>22.29123878479004</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>54.57378005981445</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>0.2817651629447937</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>0.4258251786231995</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>0.8396841287612915</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>0.04784936830401421</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>0.9045349955558777</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>0.112744927406311</v>
+      </c>
+      <c r="AM16" s="3">
+        <v>0.5181829929351807</v>
+      </c>
+      <c r="AN16" s="3">
+        <v>0.6446415185928345</v>
+      </c>
+      <c r="AO16" s="3">
+        <v>0.1559375077486038</v>
+      </c>
+      <c r="AP16" s="3">
+        <v>0.9544385671615601</v>
+      </c>
+      <c r="AQ16" s="3">
+        <v>0.999767005443573</v>
+      </c>
+      <c r="AR16" s="3">
+        <v>0.715274453163147</v>
+      </c>
+      <c r="AS16" s="3">
+        <v>0.8979763984680176</v>
+      </c>
+      <c r="AT16" s="3">
+        <v>0.7896928787231445</v>
+      </c>
+      <c r="AU16" s="3">
+        <v>-5.052856922149658</v>
+      </c>
+      <c r="AV16" s="3">
+        <v>93.01662445068359</v>
+      </c>
+      <c r="AW16" s="3">
+        <v>12.97429370880127</v>
+      </c>
+      <c r="AX16" s="3">
+        <v>417.5570000000002</v>
+      </c>
+      <c r="AY16" s="3">
+        <v>3.386200000000002</v>
+      </c>
+      <c r="AZ16" s="3">
+        <v>0.5880519362749713</v>
+      </c>
+      <c r="BA16" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB16" s="3">
+        <v>3.668249214840058</v>
+      </c>
+      <c r="BC16" s="3">
+        <v>0.7035278650177713</v>
+      </c>
+      <c r="BD16" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2037,38 +4146,163 @@
         <v>9.43</v>
       </c>
       <c r="G17" s="3">
-        <v>0.6269673212607438</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4.236110899890319</v>
+        <v>5</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I17" s="3">
-        <v>5.373032678739256</v>
+        <v>0.6269673230267181</v>
       </c>
       <c r="J17" s="3">
+        <v>4.236110917115642</v>
+      </c>
+      <c r="K17" s="3">
+        <v>5.373032676973282</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.9143198987014124</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.316068438561299</v>
+      </c>
+      <c r="N17" s="3">
+        <v>11.01512230952236</v>
+      </c>
+      <c r="O17" s="3">
+        <v>9.218476447745267</v>
+      </c>
+      <c r="P17" s="3">
+        <v>5.085680101298587</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.316068438561299</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1.971631550060213</v>
+      </c>
+      <c r="S17" s="3">
+        <v>34.18330407657724</v>
+      </c>
+      <c r="T17" s="3">
+        <v>4.466185961718441</v>
+      </c>
+      <c r="U17" s="3">
+        <v>5.705174240878733</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.316068438561299</v>
+      </c>
+      <c r="W17" s="3">
         <v>3.063400000000001</v>
       </c>
-      <c r="K17" s="3">
+      <c r="X17" s="3">
         <v>-4.869223876544572</v>
       </c>
-      <c r="L17" s="3">
+      <c r="Y17" s="3">
         <v>1.351375756442124E-05</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N17" s="3">
+      <c r="AA17" s="3">
         <v>46.68682098388672</v>
       </c>
-      <c r="O17" s="3">
+      <c r="AB17" s="3">
         <v>46.50349807739258</v>
       </c>
-      <c r="P17" s="3">
+      <c r="AC17" s="3">
         <v>40.06744003295898</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0.1574867814779282</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>0.357526034116745</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0.7977760434150696</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>0.05292394012212753</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>0.86536705493927</v>
+      </c>
+      <c r="AL17" s="3">
+        <v>0.3862963914871216</v>
+      </c>
+      <c r="AM17" s="3">
+        <v>0.5458816289901733</v>
+      </c>
+      <c r="AN17" s="3">
+        <v>0.6691522002220154</v>
+      </c>
+      <c r="AO17" s="3">
+        <v>0.2068126946687698</v>
+      </c>
+      <c r="AP17" s="3">
+        <v>0.9757220149040222</v>
+      </c>
+      <c r="AQ17" s="3">
+        <v>0.9999698400497437</v>
+      </c>
+      <c r="AR17" s="3">
+        <v>0.7815946936607361</v>
+      </c>
+      <c r="AS17" s="3">
+        <v>0.9552289843559265</v>
+      </c>
+      <c r="AT17" s="3">
+        <v>0.7651858925819397</v>
+      </c>
+      <c r="AU17" s="3">
+        <v>-4.575211524963379</v>
+      </c>
+      <c r="AV17" s="3">
+        <v>96.03324890136719</v>
+      </c>
+      <c r="AW17" s="3">
+        <v>5.789505958557129</v>
+      </c>
+      <c r="AX17" s="3">
+        <v>407.4450000000002</v>
+      </c>
+      <c r="AY17" s="3">
+        <v>3.063400000000001</v>
+      </c>
+      <c r="AZ17" s="3">
+        <v>0.7165847331452173</v>
+      </c>
+      <c r="BA17" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB17" s="3">
+        <v>3.54380626287043</v>
+      </c>
+      <c r="BC17" s="3">
+        <v>0.7173548596810633</v>
+      </c>
+      <c r="BD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2093,38 +4327,163 @@
         <v>8.23</v>
       </c>
       <c r="G18" s="3">
-        <v>0.685658451525513</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4.849069977611022</v>
+        <v>5</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I18" s="3">
-        <v>5.314341548474487</v>
+        <v>0.6856584533117636</v>
       </c>
       <c r="J18" s="3">
+        <v>4.849069997555217</v>
+      </c>
+      <c r="K18" s="3">
+        <v>5.314341546688237</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1.490813237778815</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.5151953946822857</v>
+      </c>
+      <c r="N18" s="3">
+        <v>59.84400937902042</v>
+      </c>
+      <c r="O18" s="3">
+        <v>70.99708705463284</v>
+      </c>
+      <c r="P18" s="3">
+        <v>4.509186762221185</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.5151953946822857</v>
+      </c>
+      <c r="R18" s="3">
+        <v>3.027124368635367</v>
+      </c>
+      <c r="S18" s="3">
+        <v>316.662190279133</v>
+      </c>
+      <c r="T18" s="3">
+        <v>3.499403788643906</v>
+      </c>
+      <c r="U18" s="3">
+        <v>5.518969735798465</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0.5151953946822857</v>
+      </c>
+      <c r="W18" s="3">
         <v>3.114900000000002</v>
       </c>
-      <c r="K18" s="3">
+      <c r="X18" s="3">
         <v>-5.222583116952935</v>
       </c>
-      <c r="L18" s="3">
+      <c r="Y18" s="3">
         <v>5.989862913342774E-06</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N18" s="3">
-        <v>9.347291946411133</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="AA18" s="3">
+        <v>9.347290992736816</v>
+      </c>
+      <c r="AB18" s="3">
         <v>6.190157890319824</v>
       </c>
-      <c r="P18" s="3">
+      <c r="AC18" s="3">
         <v>51.77277374267578</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0.1304218024015427</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0.6464444994926453</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0.6797714233398438</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>0.111356295645237</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>0.9288015365600586</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>0.09655777364969254</v>
+      </c>
+      <c r="AM18" s="3">
+        <v>0.1726012825965881</v>
+      </c>
+      <c r="AN18" s="3">
+        <v>0.3411219716072083</v>
+      </c>
+      <c r="AO18" s="3">
+        <v>0.3543585538864136</v>
+      </c>
+      <c r="AP18" s="3">
+        <v>0.831082820892334</v>
+      </c>
+      <c r="AQ18" s="3">
+        <v>0.9972982406616211</v>
+      </c>
+      <c r="AR18" s="3">
+        <v>0.8302739262580872</v>
+      </c>
+      <c r="AS18" s="3">
+        <v>0.8052321672439575</v>
+      </c>
+      <c r="AT18" s="3">
+        <v>0.7615982294082642</v>
+      </c>
+      <c r="AU18" s="3">
+        <v>-5.286211967468262</v>
+      </c>
+      <c r="AV18" s="3">
+        <v>91.08802032470703</v>
+      </c>
+      <c r="AW18" s="3">
+        <v>10.25955963134766</v>
+      </c>
+      <c r="AX18" s="3">
+        <v>458.4840000000002</v>
+      </c>
+      <c r="AY18" s="3">
+        <v>3.114900000000002</v>
+      </c>
+      <c r="AZ18" s="3">
+        <v>0.689595616184831</v>
+      </c>
+      <c r="BA18" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB18" s="3">
+        <v>3.42540766146798</v>
+      </c>
+      <c r="BC18" s="3">
+        <v>0.7305102598368911</v>
+      </c>
+      <c r="BD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2149,38 +4508,163 @@
         <v>10.65</v>
       </c>
       <c r="G19" s="3">
-        <v>0.6976196057554537</v>
-      </c>
-      <c r="H19" s="3">
-        <v>4.984477107800574</v>
+        <v>5</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I19" s="3">
-        <v>5.302380394244547</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J19" s="3">
+        <v>4.984477127902903</v>
+      </c>
+      <c r="K19" s="3">
+        <v>5.302380392493043</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1.039007284270767</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.3251278784817203</v>
+      </c>
+      <c r="N19" s="3">
+        <v>14.4943429083681</v>
+      </c>
+      <c r="O19" s="3">
+        <v>10.57090305404514</v>
+      </c>
+      <c r="P19" s="3">
+        <v>4.960992715729233</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.3251278784817203</v>
+      </c>
+      <c r="R19" s="3">
+        <v>2.522067132412882</v>
+      </c>
+      <c r="S19" s="3">
+        <v>47.45237197011558</v>
+      </c>
+      <c r="T19" s="3">
+        <v>4.323742073905061</v>
+      </c>
+      <c r="U19" s="3">
+        <v>5.598243357553405</v>
+      </c>
+      <c r="V19" s="3">
+        <v>0.3251278784817203</v>
+      </c>
+      <c r="W19" s="3">
         <v>3.458700000000002</v>
       </c>
-      <c r="K19" s="3">
+      <c r="X19" s="3">
         <v>-5.391947269485258</v>
       </c>
-      <c r="L19" s="3">
+      <c r="Y19" s="3">
         <v>4.055577738634562E-06</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N19" s="3">
-        <v>29.73248672485352</v>
-      </c>
-      <c r="O19" s="3">
-        <v>19.67816543579102</v>
-      </c>
-      <c r="P19" s="3">
+      <c r="AA19" s="3">
+        <v>29.73248291015625</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>19.67816925048828</v>
+      </c>
+      <c r="AC19" s="3">
         <v>82.90589904785156</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="AD19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>0.09818984568119049</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>0.232696920633316</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>0.8802070617675781</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>0.09713543951511383</v>
+      </c>
+      <c r="AK19" s="3">
+        <v>0.6800543069839478</v>
+      </c>
+      <c r="AL19" s="3">
+        <v>0.1118997782468796</v>
+      </c>
+      <c r="AM19" s="3">
+        <v>0.3822082579135895</v>
+      </c>
+      <c r="AN19" s="3">
+        <v>0.7049508094787598</v>
+      </c>
+      <c r="AO19" s="3">
+        <v>0.07699297368526459</v>
+      </c>
+      <c r="AP19" s="3">
+        <v>0.9263081550598145</v>
+      </c>
+      <c r="AQ19" s="3">
+        <v>0.9987764358520508</v>
+      </c>
+      <c r="AR19" s="3">
+        <v>0.7623728513717651</v>
+      </c>
+      <c r="AS19" s="3">
+        <v>0.8785248994827271</v>
+      </c>
+      <c r="AT19" s="3">
+        <v>0.8301860094070435</v>
+      </c>
+      <c r="AU19" s="3">
+        <v>-4.664961338043213</v>
+      </c>
+      <c r="AV19" s="3">
+        <v>98.77371215820312</v>
+      </c>
+      <c r="AW19" s="3">
+        <v>11.16911220550537</v>
+      </c>
+      <c r="AX19" s="3">
+        <v>445.5380000000002</v>
+      </c>
+      <c r="AY19" s="3">
+        <v>3.458700000000002</v>
+      </c>
+      <c r="AZ19" s="3">
+        <v>0.578604988514875</v>
+      </c>
+      <c r="BA19" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB19" s="3">
+        <v>3.576568338903403</v>
+      </c>
+      <c r="BC19" s="3">
+        <v>0.713714629010733</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE19" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="3">
         <v>1</v>
       </c>
     </row>

--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold_generic/plain/mol2mol_scaffold_generic_plain_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold_generic/plain/mol2mol_scaffold_generic_plain_generated_optimal.xlsx
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>34.03657913208008</v>
+        <v>34.03658</v>
       </c>
       <c r="AB2" s="3">
-        <v>35.33199691772461</v>
+        <v>35.331997</v>
       </c>
       <c r="AC2" s="3">
-        <v>45.15724945068359</v>
+        <v>45.15725</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -1513,55 +1513,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.4128183424472809</v>
+        <v>0.41281834</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.317070335149765</v>
+        <v>0.31707034</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.8789542317390442</v>
+        <v>0.8789542299999999</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.05042798444628716</v>
+        <v>0.050427984</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.8694758415222168</v>
+        <v>0.86947584</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.4486382901668549</v>
+        <v>0.4486383</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.7849494814872742</v>
+        <v>0.7849495</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.8201218843460083</v>
+        <v>0.8201219</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.2035863697528839</v>
+        <v>0.20358637</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.9765839576721191</v>
+        <v>0.97658396</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9999567866325378</v>
+        <v>0.9999568</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.7418512105941772</v>
+        <v>0.7418512</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.9514479637145996</v>
+        <v>0.95144796</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8597750663757324</v>
+        <v>0.85977507</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.779772758483887</v>
+        <v>-4.7797728</v>
       </c>
       <c r="AV2" s="3">
-        <v>96.93354797363281</v>
+        <v>96.93355</v>
       </c>
       <c r="AW2" s="3">
-        <v>8.543520927429199</v>
+        <v>8.543521</v>
       </c>
       <c r="AX2" s="3">
         <v>432.5240000000002</v>
@@ -1635,7 +1635,7 @@
         <v>0.5990026861033019</v>
       </c>
       <c r="N3" s="3">
-        <v>55.68607920047454</v>
+        <v>55.68607920047455</v>
       </c>
       <c r="O3" s="3">
         <v>73.79130591976713</v>
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>30.85870742797852</v>
+        <v>30.858707</v>
       </c>
       <c r="AB3" s="3">
-        <v>25.46169090270996</v>
+        <v>25.46169</v>
       </c>
       <c r="AC3" s="3">
-        <v>41.37262725830078</v>
+        <v>41.372627</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -1694,55 +1694,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.2860892415046692</v>
+        <v>0.28608924</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.5141839981079102</v>
+        <v>0.514184</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.8790133595466614</v>
+        <v>0.87901336</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.04890316352248192</v>
+        <v>0.048903164</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.9000399708747864</v>
+        <v>0.90004</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.07134749740362167</v>
+        <v>0.07134749999999999</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.3509548604488373</v>
+        <v>0.35095486</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.5367151498794556</v>
+        <v>0.53671515</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.1045412197709084</v>
+        <v>0.10454122</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9280899167060852</v>
+        <v>0.9280899</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.999531090259552</v>
+        <v>0.9995311</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.7743515372276306</v>
+        <v>0.7743515399999999</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.8736506700515747</v>
+        <v>0.87365067</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.7783913612365723</v>
+        <v>0.77839136</v>
       </c>
       <c r="AU3" s="3">
-        <v>-5.082280158996582</v>
+        <v>-5.08228</v>
       </c>
       <c r="AV3" s="3">
-        <v>96.35707092285156</v>
+        <v>96.35706999999999</v>
       </c>
       <c r="AW3" s="3">
-        <v>9.466903686523438</v>
+        <v>9.466904</v>
       </c>
       <c r="AX3" s="3">
         <v>418.5450000000002</v>
@@ -1757,7 +1757,7 @@
         <v>4</v>
       </c>
       <c r="BB3" s="3">
-        <v>3.522593138158119</v>
+        <v>3.52259313815812</v>
       </c>
       <c r="BC3" s="3">
         <v>0.7197118735379868</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>54.03302001953125</v>
+        <v>54.03302</v>
       </c>
       <c r="AB4" s="3">
-        <v>51.58975219726562</v>
+        <v>51.589752</v>
       </c>
       <c r="AC4" s="3">
-        <v>46.11929321289062</v>
+        <v>46.119293</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -1875,55 +1875,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.1514938920736313</v>
+        <v>0.15149389</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.3794129490852356</v>
+        <v>0.37941295</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.790505588054657</v>
+        <v>0.7905056</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.05281468108296394</v>
+        <v>0.05281468</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.8946078419685364</v>
+        <v>0.89460784</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.4100111424922943</v>
+        <v>0.41001114</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.6163968443870544</v>
+        <v>0.6163968399999999</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.7340325713157654</v>
+        <v>0.7340326</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.2590197920799255</v>
+        <v>0.2590198</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.9837436676025391</v>
+        <v>0.98374367</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.7540546655654907</v>
+        <v>0.75405467</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.9556649327278137</v>
+        <v>0.95566493</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.8375112414360046</v>
+        <v>0.83751124</v>
       </c>
       <c r="AU4" s="3">
-        <v>-4.578262329101562</v>
+        <v>-4.5782623</v>
       </c>
       <c r="AV4" s="3">
-        <v>98.41603851318359</v>
+        <v>98.41604</v>
       </c>
       <c r="AW4" s="3">
-        <v>6.461910247802734</v>
+        <v>6.4619102</v>
       </c>
       <c r="AX4" s="3">
         <v>421.4720000000002</v>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>54.02364349365234</v>
+        <v>54.023643</v>
       </c>
       <c r="AB5" s="3">
-        <v>51.60739898681641</v>
+        <v>51.6074</v>
       </c>
       <c r="AC5" s="3">
-        <v>46.01803207397461</v>
+        <v>46.018032</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -2056,55 +2056,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.1515597552061081</v>
+        <v>0.15155976</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.3794240057468414</v>
+        <v>0.379424</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.7904849052429199</v>
+        <v>0.7904849</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.0527871735394001</v>
+        <v>0.052787174</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.8945648074150085</v>
+        <v>0.8945648</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.4096334874629974</v>
+        <v>0.4096335</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.6159687638282776</v>
+        <v>0.61596876</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.7336847186088562</v>
+        <v>0.7336847</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.2587461173534393</v>
+        <v>0.25874612</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.9837337732315063</v>
+        <v>0.9837338</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.7541525363922119</v>
+        <v>0.75415254</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.955665111541748</v>
+        <v>0.9556651</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.8373624086380005</v>
+        <v>0.8373624</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.578091621398926</v>
+        <v>-4.5780916</v>
       </c>
       <c r="AV5" s="3">
-        <v>98.40773010253906</v>
+        <v>98.40773</v>
       </c>
       <c r="AW5" s="3">
-        <v>6.452359199523926</v>
+        <v>6.452359</v>
       </c>
       <c r="AX5" s="3">
         <v>420.4749380000002</v>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>10.30675029754639</v>
+        <v>10.30675</v>
       </c>
       <c r="AB6" s="3">
-        <v>4.953838348388672</v>
+        <v>4.9538383</v>
       </c>
       <c r="AC6" s="3">
-        <v>63.28201293945312</v>
+        <v>63.282013</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -2237,55 +2237,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.172451987862587</v>
+        <v>0.17245199</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.6441282033920288</v>
+        <v>0.6441282</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.6298868656158447</v>
+        <v>0.62988687</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.09360764920711517</v>
+        <v>0.09360765</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.9688534736633301</v>
+        <v>0.9688535</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.2428222149610519</v>
+        <v>0.24282221</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.2800058722496033</v>
+        <v>0.28000587</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.3691545128822327</v>
+        <v>0.3691545</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.5387910604476929</v>
+        <v>0.53879106</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9079670906066895</v>
+        <v>0.9079671</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9994224309921265</v>
+        <v>0.99942243</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.8015594482421875</v>
+        <v>0.80155945</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.8959123492240906</v>
+        <v>0.89591235</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.8629838824272156</v>
+        <v>0.8629839</v>
       </c>
       <c r="AU6" s="3">
-        <v>-5.264070510864258</v>
+        <v>-5.2640705</v>
       </c>
       <c r="AV6" s="3">
-        <v>90.62617492675781</v>
+        <v>90.626175</v>
       </c>
       <c r="AW6" s="3">
-        <v>15.84818458557129</v>
+        <v>15.848185</v>
       </c>
       <c r="AX6" s="3">
         <v>430.4740000000002</v>
@@ -2386,7 +2386,7 @@
         <v>0.5885768164687759</v>
       </c>
       <c r="W7" s="3">
-        <v>3.286700000000002</v>
+        <v>3.286700000000001</v>
       </c>
       <c r="X7" s="3">
         <v>-5.183149985103853</v>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>62.00168609619141</v>
+        <v>62.001686</v>
       </c>
       <c r="AB7" s="3">
-        <v>58.01309204101562</v>
+        <v>58.013092</v>
       </c>
       <c r="AC7" s="3">
-        <v>53.0703010559082</v>
+        <v>53.0703</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -2418,61 +2418,61 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.3010247945785522</v>
+        <v>0.3010248</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.3763807415962219</v>
+        <v>0.37638074</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.85511714220047</v>
+        <v>0.8551171400000001</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.07315777242183685</v>
+        <v>0.07315777</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.8861689567565918</v>
+        <v>0.88616896</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.2670863270759583</v>
+        <v>0.26708633</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.620905339717865</v>
+        <v>0.62090534</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.7570825815200806</v>
+        <v>0.7570826</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.1881253570318222</v>
+        <v>0.18812536</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9700537919998169</v>
+        <v>0.9700538</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.9998720288276672</v>
+        <v>0.999872</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.743526816368103</v>
+        <v>0.7435268</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9412748217582703</v>
+        <v>0.9412748</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.8953615427017212</v>
+        <v>0.89536154</v>
       </c>
       <c r="AU7" s="3">
-        <v>-4.690360069274902</v>
+        <v>-4.69036</v>
       </c>
       <c r="AV7" s="3">
-        <v>101.8853302001953</v>
+        <v>101.88533</v>
       </c>
       <c r="AW7" s="3">
-        <v>6.763211250305176</v>
+        <v>6.7632113</v>
       </c>
       <c r="AX7" s="3">
         <v>432.5240000000002</v>
       </c>
       <c r="AY7" s="3">
-        <v>3.286700000000002</v>
+        <v>3.286700000000001</v>
       </c>
       <c r="AZ7" s="3">
         <v>0.4537042148229764</v>
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>57.12314987182617</v>
+        <v>57.12315</v>
       </c>
       <c r="AB8" s="3">
-        <v>53.15890502929688</v>
+        <v>53.158905</v>
       </c>
       <c r="AC8" s="3">
-        <v>59.37638473510742</v>
+        <v>59.376385</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -2599,55 +2599,55 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.2634467482566833</v>
+        <v>0.26344675</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.3268089890480042</v>
+        <v>0.326809</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.8230131864547729</v>
+        <v>0.8230132</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.09272345155477524</v>
+        <v>0.09272345</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.7996328473091125</v>
+        <v>0.79963285</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.3018380403518677</v>
+        <v>0.30183804</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.4526433348655701</v>
+        <v>0.45264333</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.5517083406448364</v>
+        <v>0.55170834</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.1512510031461716</v>
+        <v>0.151251</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9123425483703613</v>
+        <v>0.91234255</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.9997068643569946</v>
+        <v>0.99970686</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.7845497727394104</v>
+        <v>0.7845498</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.9428170919418335</v>
+        <v>0.9428171</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.8034658432006836</v>
+        <v>0.80346584</v>
       </c>
       <c r="AU8" s="3">
-        <v>-4.516212463378906</v>
+        <v>-4.5162125</v>
       </c>
       <c r="AV8" s="3">
-        <v>98.88426971435547</v>
+        <v>98.88427</v>
       </c>
       <c r="AW8" s="3">
-        <v>7.63823413848877</v>
+        <v>7.638234</v>
       </c>
       <c r="AX8" s="3">
         <v>421.4720000000002</v>
@@ -2762,13 +2762,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>50.9268913269043</v>
+        <v>50.92689</v>
       </c>
       <c r="AB9" s="3">
-        <v>50.9757194519043</v>
+        <v>50.97572</v>
       </c>
       <c r="AC9" s="3">
-        <v>40.63362884521484</v>
+        <v>40.63363</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -2780,55 +2780,55 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.2754431366920471</v>
+        <v>0.27544314</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.2086796313524246</v>
+        <v>0.20867963</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.9090962409973145</v>
+        <v>0.90909624</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.06169123575091362</v>
+        <v>0.061691236</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.7485303282737732</v>
+        <v>0.7485303</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.2723854780197144</v>
+        <v>0.27238548</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.656551718711853</v>
+        <v>0.6565517</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.7990891337394714</v>
+        <v>0.79908913</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.1086594834923744</v>
+        <v>0.10865948</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.9628103375434875</v>
+        <v>0.96281034</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.9999311566352844</v>
+        <v>0.99993116</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.7291480302810669</v>
+        <v>0.7291480299999999</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.9398983120918274</v>
+        <v>0.9398983</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.8420951962471008</v>
+        <v>0.8420952</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.587052822113037</v>
+        <v>-4.587053</v>
       </c>
       <c r="AV9" s="3">
-        <v>98.45797729492188</v>
+        <v>98.45798000000001</v>
       </c>
       <c r="AW9" s="3">
-        <v>5.001123428344727</v>
+        <v>5.0011234</v>
       </c>
       <c r="AX9" s="3">
         <v>442.5190000000002</v>
@@ -2908,7 +2908,7 @@
         <v>76.0808612751983</v>
       </c>
       <c r="P10" s="3">
-        <v>4.797356000773195</v>
+        <v>4.797356000773196</v>
       </c>
       <c r="Q10" s="3">
         <v>0.6027867767415637</v>
@@ -2920,7 +2920,7 @@
         <v>242.1620484371657</v>
       </c>
       <c r="T10" s="3">
-        <v>3.61589391835973</v>
+        <v>3.615893918359729</v>
       </c>
       <c r="U10" s="3">
         <v>5.97881808318666</v>
@@ -2943,13 +2943,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>59.47089767456055</v>
+        <v>59.470898</v>
       </c>
       <c r="AB10" s="3">
-        <v>57.21721267700195</v>
+        <v>57.217213</v>
       </c>
       <c r="AC10" s="3">
-        <v>40.80253219604492</v>
+        <v>40.802532</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -2961,55 +2961,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.1844686567783356</v>
+        <v>0.18446866</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.420243501663208</v>
+        <v>0.4202435</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.8358315229415894</v>
+        <v>0.8358314999999999</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.04515016451478004</v>
+        <v>0.045150165</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.9386307001113892</v>
+        <v>0.9386307</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.4181108474731445</v>
+        <v>0.41811085</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.7442826628684998</v>
+        <v>0.74428266</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.8617993593215942</v>
+        <v>0.86179936</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.2975648641586304</v>
+        <v>0.29756486</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.9936869740486145</v>
+        <v>0.993687</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9999872446060181</v>
+        <v>0.9999872400000001</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.7217900156974792</v>
+        <v>0.72179</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.9570225477218628</v>
+        <v>0.95702255</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.9055355191230774</v>
+        <v>0.9055355</v>
       </c>
       <c r="AU10" s="3">
-        <v>-4.767285823822021</v>
+        <v>-4.767286</v>
       </c>
       <c r="AV10" s="3">
-        <v>101.1879043579102</v>
+        <v>101.187904</v>
       </c>
       <c r="AW10" s="3">
-        <v>5.748510837554932</v>
+        <v>5.748511</v>
       </c>
       <c r="AX10" s="3">
         <v>432.5240000000002</v>
@@ -3083,7 +3083,7 @@
         <v>0.5538972903245317</v>
       </c>
       <c r="N11" s="3">
-        <v>52.85744973393292</v>
+        <v>52.85744973393293</v>
       </c>
       <c r="O11" s="3">
         <v>73.97049186169482</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>39.75580978393555</v>
+        <v>39.75581</v>
       </c>
       <c r="AB11" s="3">
-        <v>32.81678771972656</v>
+        <v>32.816788</v>
       </c>
       <c r="AC11" s="3">
-        <v>42.63827133178711</v>
+        <v>42.63827</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -3142,55 +3142,55 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.3349597156047821</v>
+        <v>0.33495972</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.4971658289432526</v>
+        <v>0.49716583</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.8305774927139282</v>
+        <v>0.8305775</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.05206185579299927</v>
+        <v>0.052061856</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.9213895797729492</v>
+        <v>0.9213896</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.2205078303813934</v>
+        <v>0.22050783</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.4619075357913971</v>
+        <v>0.46190754</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.5620790719985962</v>
+        <v>0.5620791000000001</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.1509415060281754</v>
+        <v>0.1509415</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.957487940788269</v>
+        <v>0.95748794</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9998504519462585</v>
+        <v>0.9998504499999999</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.8074136972427368</v>
+        <v>0.8074137</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.9490911364555359</v>
+        <v>0.9490911400000001</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.8077398538589478</v>
+        <v>0.80773985</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.965895175933838</v>
+        <v>-4.965895</v>
       </c>
       <c r="AV11" s="3">
-        <v>95.56562805175781</v>
+        <v>95.56563</v>
       </c>
       <c r="AW11" s="3">
-        <v>10.71188068389893</v>
+        <v>10.711881</v>
       </c>
       <c r="AX11" s="3">
         <v>417.5570000000001</v>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>24.80001449584961</v>
+        <v>24.800014</v>
       </c>
       <c r="AB12" s="3">
-        <v>23.34781265258789</v>
+        <v>23.347813</v>
       </c>
       <c r="AC12" s="3">
-        <v>43.05011367797852</v>
+        <v>43.050114</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -3323,55 +3323,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.3229777216911316</v>
+        <v>0.32297772</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.4890483915805817</v>
+        <v>0.4890484</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.8431566953659058</v>
+        <v>0.8431567</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.04133586958050728</v>
+        <v>0.04133587</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.8974877595901489</v>
+        <v>0.89748776</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.08953447639942169</v>
+        <v>0.08953448</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.3851622939109802</v>
+        <v>0.3851623</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.4774286150932312</v>
+        <v>0.47742862</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.1085920929908752</v>
+        <v>0.10859209</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.9089075326919556</v>
+        <v>0.90890753</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9997041821479797</v>
+        <v>0.9997042</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.7743037939071655</v>
+        <v>0.7743038</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.8871881365776062</v>
+        <v>0.88718814</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.6713687181472778</v>
+        <v>0.6713687</v>
       </c>
       <c r="AU12" s="3">
-        <v>-5.05207347869873</v>
+        <v>-5.0520735</v>
       </c>
       <c r="AV12" s="3">
-        <v>93.55834197998047</v>
+        <v>93.55834</v>
       </c>
       <c r="AW12" s="3">
-        <v>10.05699634552002</v>
+        <v>10.056996</v>
       </c>
       <c r="AX12" s="3">
         <v>403.5300000000001</v>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>20.17489242553711</v>
+        <v>20.174892</v>
       </c>
       <c r="AB13" s="3">
-        <v>23.7639102935791</v>
+        <v>23.76391</v>
       </c>
       <c r="AC13" s="3">
-        <v>56.34565353393555</v>
+        <v>56.345654</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -3504,55 +3504,55 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.4605282247066498</v>
+        <v>0.46052822</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.4387226998806</v>
+        <v>0.4387227</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.8704509735107422</v>
+        <v>0.870451</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.05935602262616158</v>
+        <v>0.059356023</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.8431379199028015</v>
+        <v>0.8431379</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.1032470613718033</v>
+        <v>0.10324706</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.3283776640892029</v>
+        <v>0.32837766</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.442185640335083</v>
+        <v>0.44218564</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.0779731422662735</v>
+        <v>0.07797314</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.8376519083976746</v>
+        <v>0.8376519</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9987085461616516</v>
+        <v>0.99870855</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.7852612137794495</v>
+        <v>0.7852612</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.8799749612808228</v>
+        <v>0.87997496</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.7288599014282227</v>
+        <v>0.7288599</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.895804405212402</v>
+        <v>-4.8958044</v>
       </c>
       <c r="AV13" s="3">
-        <v>96.39573669433594</v>
+        <v>96.39574</v>
       </c>
       <c r="AW13" s="3">
-        <v>11.46587753295898</v>
+        <v>11.465878</v>
       </c>
       <c r="AX13" s="3">
         <v>403.5300000000001</v>
@@ -3644,7 +3644,7 @@
         <v>263.3697977917691</v>
       </c>
       <c r="T14" s="3">
-        <v>3.579434029694775</v>
+        <v>3.579434029694774</v>
       </c>
       <c r="U14" s="3">
         <v>5.87457892317879</v>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>22.13141822814941</v>
+        <v>22.131418</v>
       </c>
       <c r="AB14" s="3">
-        <v>26.04515075683594</v>
+        <v>26.04515</v>
       </c>
       <c r="AC14" s="3">
-        <v>48.23393630981445</v>
+        <v>48.233936</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -3685,55 +3685,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.3091988861560822</v>
+        <v>0.3091989</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.4710089564323425</v>
+        <v>0.47100896</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.8624054193496704</v>
+        <v>0.8624054</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.03987503796815872</v>
+        <v>0.039875038</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.9063378572463989</v>
+        <v>0.9063378600000001</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.1281423568725586</v>
+        <v>0.12814236</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.429051548242569</v>
+        <v>0.42905155</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.5838853120803833</v>
+        <v>0.5838853000000001</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.1096794605255127</v>
+        <v>0.10967946</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.9557859301567078</v>
+        <v>0.95578593</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9998464584350586</v>
+        <v>0.99984646</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.7801386713981628</v>
+        <v>0.7801387</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.9159609079360962</v>
+        <v>0.9159609</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.7508474588394165</v>
+        <v>0.75084746</v>
       </c>
       <c r="AU14" s="3">
-        <v>-5.046236991882324</v>
+        <v>-5.046237</v>
       </c>
       <c r="AV14" s="3">
-        <v>94.6217041015625</v>
+        <v>94.62170399999999</v>
       </c>
       <c r="AW14" s="3">
-        <v>10.82663440704346</v>
+        <v>10.826634</v>
       </c>
       <c r="AX14" s="3">
         <v>403.5300000000001</v>
@@ -3801,7 +3801,7 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L15" s="3">
-        <v>1.284913747638275</v>
+        <v>1.284913747638276</v>
       </c>
       <c r="M15" s="3">
         <v>0.5897994585461864</v>
@@ -3840,7 +3840,7 @@
         <v>-5.163112760649854</v>
       </c>
       <c r="Y15" s="3">
-        <v>6.868900720401071E-06</v>
+        <v>6.868900720401072E-06</v>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
@@ -3848,13 +3848,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>29.61392211914062</v>
+        <v>29.613922</v>
       </c>
       <c r="AB15" s="3">
-        <v>28.70643997192383</v>
+        <v>28.70644</v>
       </c>
       <c r="AC15" s="3">
-        <v>54.54449462890625</v>
+        <v>54.544495</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -3866,55 +3866,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.290806919336319</v>
+        <v>0.29080692</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.5101267099380493</v>
+        <v>0.5101267</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.8653945922851562</v>
+        <v>0.8653946</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.04396987706422806</v>
+        <v>0.043969877</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.9301586151123047</v>
+        <v>0.9301585999999999</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.09436273574829102</v>
+        <v>0.094362736</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.4396128058433533</v>
+        <v>0.4396128</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.589055597782135</v>
+        <v>0.5890556</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.1086192578077316</v>
+        <v>0.10861926</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.9567853808403015</v>
+        <v>0.9567854</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9997827410697937</v>
+        <v>0.99978274</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.7906284332275391</v>
+        <v>0.79062843</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.9222062826156616</v>
+        <v>0.9222063</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.8188015222549438</v>
+        <v>0.8188015</v>
       </c>
       <c r="AU15" s="3">
-        <v>-5.051095962524414</v>
+        <v>-5.051096</v>
       </c>
       <c r="AV15" s="3">
-        <v>96.21928405761719</v>
+        <v>96.219284</v>
       </c>
       <c r="AW15" s="3">
-        <v>12.13404369354248</v>
+        <v>12.134044</v>
       </c>
       <c r="AX15" s="3">
         <v>417.5570000000002</v>
@@ -3988,7 +3988,7 @@
         <v>0.5902141860166523</v>
       </c>
       <c r="N16" s="3">
-        <v>51.52935574146495</v>
+        <v>51.52935574146496</v>
       </c>
       <c r="O16" s="3">
         <v>74.72757378714228</v>
@@ -4021,7 +4021,7 @@
         <v>-5.163112760649856</v>
       </c>
       <c r="Y16" s="3">
-        <v>6.868900720401043E-06</v>
+        <v>6.868900720401044E-06</v>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
@@ -4029,13 +4029,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>24.38673973083496</v>
+        <v>24.38674</v>
       </c>
       <c r="AB16" s="3">
-        <v>22.29123878479004</v>
+        <v>22.291239</v>
       </c>
       <c r="AC16" s="3">
-        <v>54.57378005981445</v>
+        <v>54.57378</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -4047,55 +4047,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.2817651629447937</v>
+        <v>0.28176516</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.4258251786231995</v>
+        <v>0.42582518</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.8396841287612915</v>
+        <v>0.8396841</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.04784936830401421</v>
+        <v>0.04784937</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.9045349955558777</v>
+        <v>0.904535</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.112744927406311</v>
+        <v>0.11274493</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.5181829929351807</v>
+        <v>0.5181829999999999</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.6446415185928345</v>
+        <v>0.6446415</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.1559375077486038</v>
+        <v>0.15593751</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.9544385671615601</v>
+        <v>0.95443857</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.999767005443573</v>
+        <v>0.999767</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.715274453163147</v>
+        <v>0.71527445</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.8979763984680176</v>
+        <v>0.8979764</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.7896928787231445</v>
+        <v>0.7896929</v>
       </c>
       <c r="AU16" s="3">
-        <v>-5.052856922149658</v>
+        <v>-5.052857</v>
       </c>
       <c r="AV16" s="3">
-        <v>93.01662445068359</v>
+        <v>93.01662399999999</v>
       </c>
       <c r="AW16" s="3">
-        <v>12.97429370880127</v>
+        <v>12.974294</v>
       </c>
       <c r="AX16" s="3">
         <v>417.5570000000002</v>
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>46.68682098388672</v>
+        <v>46.68682</v>
       </c>
       <c r="AB17" s="3">
-        <v>46.50349807739258</v>
+        <v>46.503498</v>
       </c>
       <c r="AC17" s="3">
-        <v>40.06744003295898</v>
+        <v>40.06744</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -4228,55 +4228,55 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.1574867814779282</v>
+        <v>0.15748678</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.357526034116745</v>
+        <v>0.35752603</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.7977760434150696</v>
+        <v>0.79777604</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.05292394012212753</v>
+        <v>0.05292394</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.86536705493927</v>
+        <v>0.86536705</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.3862963914871216</v>
+        <v>0.3862964</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.5458816289901733</v>
+        <v>0.5458816</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.6691522002220154</v>
+        <v>0.6691522</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.2068126946687698</v>
+        <v>0.2068127</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.9757220149040222</v>
+        <v>0.975722</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9999698400497437</v>
+        <v>0.99996984</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.7815946936607361</v>
+        <v>0.7815947</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.9552289843559265</v>
+        <v>0.955229</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.7651858925819397</v>
+        <v>0.7651859</v>
       </c>
       <c r="AU17" s="3">
-        <v>-4.575211524963379</v>
+        <v>-4.5752115</v>
       </c>
       <c r="AV17" s="3">
-        <v>96.03324890136719</v>
+        <v>96.03325</v>
       </c>
       <c r="AW17" s="3">
-        <v>5.789505958557129</v>
+        <v>5.789506</v>
       </c>
       <c r="AX17" s="3">
         <v>407.4450000000002</v>
@@ -4391,13 +4391,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>9.347290992736816</v>
+        <v>9.347291</v>
       </c>
       <c r="AB18" s="3">
-        <v>6.190157890319824</v>
+        <v>6.190158</v>
       </c>
       <c r="AC18" s="3">
-        <v>51.77277374267578</v>
+        <v>51.772774</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -4409,55 +4409,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.1304218024015427</v>
+        <v>0.1304218</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.6464444994926453</v>
+        <v>0.6464445</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.6797714233398438</v>
+        <v>0.6797714</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.111356295645237</v>
+        <v>0.111356296</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.9288015365600586</v>
+        <v>0.92880154</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.09655777364969254</v>
+        <v>0.09655777</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.1726012825965881</v>
+        <v>0.17260128</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.3411219716072083</v>
+        <v>0.34112197</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.3543585538864136</v>
+        <v>0.35435855</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.831082820892334</v>
+        <v>0.8310828</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9972982406616211</v>
+        <v>0.99729824</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.8302739262580872</v>
+        <v>0.8302739</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.8052321672439575</v>
+        <v>0.80523217</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.7615982294082642</v>
+        <v>0.7615982</v>
       </c>
       <c r="AU18" s="3">
-        <v>-5.286211967468262</v>
+        <v>-5.286212</v>
       </c>
       <c r="AV18" s="3">
-        <v>91.08802032470703</v>
+        <v>91.08802</v>
       </c>
       <c r="AW18" s="3">
-        <v>10.25955963134766</v>
+        <v>10.25956</v>
       </c>
       <c r="AX18" s="3">
         <v>458.4840000000002</v>
@@ -4528,7 +4528,7 @@
         <v>1.039007284270767</v>
       </c>
       <c r="M19" s="3">
-        <v>0.3251278784817203</v>
+        <v>0.3251278784817202</v>
       </c>
       <c r="N19" s="3">
         <v>14.4943429083681</v>
@@ -4540,7 +4540,7 @@
         <v>4.960992715729233</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.3251278784817203</v>
+        <v>0.3251278784817202</v>
       </c>
       <c r="R19" s="3">
         <v>2.522067132412882</v>
@@ -4555,7 +4555,7 @@
         <v>5.598243357553405</v>
       </c>
       <c r="V19" s="3">
-        <v>0.3251278784817203</v>
+        <v>0.3251278784817202</v>
       </c>
       <c r="W19" s="3">
         <v>3.458700000000002</v>
@@ -4572,13 +4572,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>29.73248291015625</v>
+        <v>29.732483</v>
       </c>
       <c r="AB19" s="3">
-        <v>19.67816925048828</v>
+        <v>19.67817</v>
       </c>
       <c r="AC19" s="3">
-        <v>82.90589904785156</v>
+        <v>82.9059</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -4590,55 +4590,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.09818984568119049</v>
+        <v>0.098189846</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.232696920633316</v>
+        <v>0.23269692</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.8802070617675781</v>
+        <v>0.88020706</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.09713543951511383</v>
+        <v>0.09713544</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.6800543069839478</v>
+        <v>0.6800543</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.1118997782468796</v>
+        <v>0.11189978</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.3822082579135895</v>
+        <v>0.38220826</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.7049508094787598</v>
+        <v>0.7049508</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.07699297368526459</v>
+        <v>0.07699296999999999</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.9263081550598145</v>
+        <v>0.92630816</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9987764358520508</v>
+        <v>0.99877644</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.7623728513717651</v>
+        <v>0.76237285</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.8785248994827271</v>
+        <v>0.8785249000000001</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.8301860094070435</v>
+        <v>0.830186</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.664961338043213</v>
+        <v>-4.6649613</v>
       </c>
       <c r="AV19" s="3">
-        <v>98.77371215820312</v>
+        <v>98.77370999999999</v>
       </c>
       <c r="AW19" s="3">
-        <v>11.16911220550537</v>
+        <v>11.169112</v>
       </c>
       <c r="AX19" s="3">
         <v>445.5380000000002</v>
